--- a/別紙/別紙E1_対応表各種.xlsx
+++ b/別紙/別紙E1_対応表各種.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="56300" yWindow="-3680" windowWidth="42180" windowHeight="23600" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-35440" yWindow="8040" windowWidth="33600" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="別紙1_ETRCARS_インシデント対応詳細表" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <definedName name="A" localSheetId="0">#REF!</definedName>
     <definedName name="TABLE" localSheetId="0">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="181029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -56,13 +56,6 @@
       <family val="3"/>
       <color theme="1"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="游ゴシック"/>
-      <charset val="128"/>
-      <family val="3"/>
-      <sz val="6"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="游ゴシック"/>
@@ -148,11 +141,22 @@
       <sz val="18"/>
     </font>
     <font>
+      <name val="MeiryoUI"/>
+      <charset val="128"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="MeiryoUI"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <u val="single"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -161,8 +165,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
-        <bgColor rgb="00305496"/>
+        <fgColor rgb="FF305496"/>
+        <bgColor rgb="FF305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E3"/>
+        <bgColor rgb="00D5F5E3"/>
       </patternFill>
     </fill>
   </fills>
@@ -310,13 +320,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+  <cellStyleXfs count="3">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -344,15 +357,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -379,10 +392,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -391,15 +404,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -408,10 +421,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -432,34 +445,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -469,11 +482,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="1"/>
+    <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -880,7 +898,8 @@
     <col width="29.28515625" bestFit="1" customWidth="1" style="9" min="7" max="7"/>
     <col width="32.42578125" bestFit="1" customWidth="1" style="9" min="8" max="8"/>
     <col width="13.28515625" customWidth="1" style="9" min="9" max="9"/>
-    <col width="7.5703125" customWidth="1" style="9" min="10" max="16384"/>
+    <col width="7.5703125" customWidth="1" style="9" min="10" max="10"/>
+    <col width="7.5703125" customWidth="1" style="9" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="53">
@@ -1158,12 +1177,6 @@
       <c r="D16" s="21" t="n"/>
     </row>
     <row r="17" ht="39" customHeight="1" s="53">
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="9" t="n"/>
       <c r="I17" s="17" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1" s="53">
@@ -3232,7 +3245,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Wai Yan Aung</t>
+          <t>Vilaphong Douangmala</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -3246,9 +3259,9 @@
         </is>
       </c>
       <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>waiyan.a@codium.co</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>liang@codium.co</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3311,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Vilaphong Douangmala</t>
+          <t xml:space="preserve"> Sovannit Oun    </t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -3312,9 +3325,75 @@
         </is>
       </c>
       <c r="H17" s="4" t="n"/>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>liang@codium.co</t>
+      <c r="I17" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  sovannit.o@codium.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="56" t="inlineStr">
+        <is>
+          <t>CODIUM Co., Ltd.（タイ）</t>
+        </is>
+      </c>
+      <c r="D18" s="56" t="inlineStr">
+        <is>
+          <t>JP開発チーム</t>
+        </is>
+      </c>
+      <c r="E18" s="56" t="inlineStr">
+        <is>
+          <t>Suthichai Chukaew</t>
+        </is>
+      </c>
+      <c r="F18" s="56" t="inlineStr">
+        <is>
+          <t>開発担当</t>
+        </is>
+      </c>
+      <c r="G18" s="56" t="inlineStr">
+        <is>
+          <t>CODIUM開発</t>
+        </is>
+      </c>
+      <c r="H18" s="56" t="inlineStr"/>
+      <c r="I18" s="56" t="inlineStr">
+        <is>
+          <t>suthichai.c@codium.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="56" t="inlineStr">
+        <is>
+          <t>CODIUM Co., Ltd.（タイ）</t>
+        </is>
+      </c>
+      <c r="D19" s="56" t="inlineStr">
+        <is>
+          <t>JP開発チーム</t>
+        </is>
+      </c>
+      <c r="E19" s="56" t="inlineStr">
+        <is>
+          <t>Saw Zaw Myo Htet Ko</t>
+        </is>
+      </c>
+      <c r="F19" s="56" t="inlineStr">
+        <is>
+          <t>開発担当</t>
+        </is>
+      </c>
+      <c r="G19" s="56" t="inlineStr">
+        <is>
+          <t>CODIUM開発</t>
+        </is>
+      </c>
+      <c r="H19" s="56" t="inlineStr"/>
+      <c r="I19" s="56" t="inlineStr">
+        <is>
+          <t>saw.k@codium.co</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3681,8 @@
     <col width="22.140625" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
     <col width="16.7109375" customWidth="1" style="10" min="8" max="8"/>
     <col width="28.5703125" customWidth="1" style="10" min="9" max="9"/>
-    <col width="10.7109375" customWidth="1" style="10" min="10" max="16384"/>
+    <col width="10.7109375" customWidth="1" style="10" min="10" max="10"/>
+    <col width="10.7109375" customWidth="1" style="10" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="3" ht="31" customHeight="1" s="53">
@@ -4431,7 +4511,8 @@
     <col width="10.7109375" customWidth="1" style="10" min="1" max="1"/>
     <col width="20.42578125" customWidth="1" style="10" min="2" max="2"/>
     <col width="89.140625" customWidth="1" style="10" min="3" max="3"/>
-    <col width="10.7109375" customWidth="1" style="10" min="4" max="16384"/>
+    <col width="10.7109375" customWidth="1" style="10" min="4" max="4"/>
+    <col width="10.7109375" customWidth="1" style="10" min="5" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="21" customHeight="1" s="53">
@@ -5002,7 +5083,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F93"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="18"/>
   <cols>
     <col width="4" customWidth="1" style="53" min="1" max="1"/>
     <col width="28" customWidth="1" style="53" min="2" max="2"/>
@@ -5045,403 +5126,403 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>AWS 運用全般（現状は他ボードに分散）</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>活用度低</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>AWSアカウント使用申請</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>アカウント申請・棚卸し</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>P-015 強権限利用記録と連動</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>AWS設定変更/パッチ適応</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>AWS 設定変更・パッチ適用 ※ボード名「適応」要修正（P-???、Trello側）</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" s="0" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>ETR-BUY</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>ETR-BUY 関連</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>活用度低</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>インシデント報告</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>障害対応／インシデント全般</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>ドキュメント「障害対応ボード」「Trello 障害ボード」「インシデント報告ボード」は本ボード</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>デザイン修正</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>UI／デザイン修正</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" s="0" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>テスト</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>テスト用</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>活用度低</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>バグ修正</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>バグ修正</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" s="0" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>マスター関連</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>マスタデータ管理</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" s="0" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>ユーザーへの告知</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>ユーザー通知</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>メンテナンス通知等</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>改修</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>既存機能改修</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>ドキュメント「開発管理ボード」と関連</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>監査報告</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>月次／四半期／年次／現地監査・パッチ／ログ／脆弱性報告</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>ドキュメント「監査ボード」「監査報告ボード」「現地監査ボード」「年次監査ボード」「月次点検ボード」「監視報告ボード」「改善報告ボード」はすべて本ボード（リストで区別）</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>承認ルール</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>承認フロー定義</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" s="0" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>新規開発</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>新規機能開発</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="0" t="inlineStr">
         <is>
           <t>ドキュメント「開発管理ボード」と関連</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>操作マニュアル</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>操作マニュアル管理</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" s="0" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>─── リスト構成（各ボード内） ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─ ─</t>
         </is>
@@ -5472,1188 +5553,1188 @@
       <c r="F19" s="54" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>AWSアカウント使用申請</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>root SB</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" s="0" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>AWSアカウント使用申請</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>本番　SB  IAM(強）</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" s="0" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>AWSアカウント使用申請</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>本番　SB 運用</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" s="0" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>AWSアカウント使用申請</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>本番　CODIUM 　（Liang）</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" s="0" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>AWSアカウント使用申請</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>本番　CODIUM（MO）運用</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" s="0" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>AWSアカウント使用申請</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>ステージング　CODIUM （強）</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" s="0" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>AWSアカウント使用申請</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>RDS アクセス申請</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" s="0" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>AWS設定変更/パッチ適応</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>案件</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" s="0" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>AWS設定変更/パッチ適応</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>変更計画/見積/承認</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" s="0" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>AWS設定変更/パッチ適応</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>変更確認/承認</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" s="0" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>AWS設定変更/パッチ適応</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>パッチ適応</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" s="0" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>インシデント報告</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>軽度</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" s="0" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>インシデント報告</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>中度</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" s="0" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>インシデント報告</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>重度</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" s="0" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>インシデント報告</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>【開発版】本番実装承認</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" s="0" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>インシデント報告</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>【本番】実装依頼中</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" s="0" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>インシデント報告</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>【本番】完成検査/承認</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" s="0" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
         <is>
           <t>デザイン修正</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>①案件/要件定義</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" s="0" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>デザイン修正</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>②【開発】修正依頼中</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" s="0" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>デザイン修正</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>③【開発】修正確認</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" s="0" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>デザイン修正</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>④【ステージング】修正確認</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" s="0" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>デザイン修正</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>⑤【ステージング】本番実装承認</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" s="0" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>デザイン修正</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>⑥【本番】実装依頼中</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" s="0" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
         <is>
           <t>デザイン修正</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>⑦【本番】完成検査/承認</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" s="0" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="0" t="inlineStr">
         <is>
           <t>デザイン修正</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>⑧完了済み</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" s="0" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="0" t="inlineStr">
         <is>
           <t>バグ修正</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>①案件/要件定義</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" s="0" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="0" t="inlineStr">
         <is>
           <t>バグ修正</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>①-1 仕様改修案件</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" s="0" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="0" t="inlineStr">
         <is>
           <t>バグ修正</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>②【ETR様】修正内容の確認</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" s="0" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="0" t="inlineStr">
         <is>
           <t>バグ修正</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>③【CODIUM】修正内容の確認</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" s="0" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
         <is>
           <t>バグ修正</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>④【開発】修正依頼中</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" s="0" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
         <is>
           <t>バグ修正</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>⑤【開発】修正確認</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" s="0" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
         <is>
           <t>バグ修正</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>⑥【ステージング】修正確認</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" s="0" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="0" t="inlineStr">
         <is>
           <t>バグ修正</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>⑦【ステージング】本番実装承認</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" s="0" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="0" t="inlineStr">
         <is>
           <t>バグ修正</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>⑧【本番】実装依頼中</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" s="0" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="0" t="inlineStr">
         <is>
           <t>バグ修正</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>⑨【本番】完成検査/承認</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="0" t="n">
         <v>187</v>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" s="0" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="0" t="inlineStr">
         <is>
           <t>バグ修正</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>⑩完了済み</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="0" t="n">
         <v>147</v>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" s="0" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="0" t="inlineStr">
         <is>
           <t>マスター関連</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>案件</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" s="0" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="0" t="inlineStr">
         <is>
           <t>マスター関連</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="0" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" s="0" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="0" t="inlineStr">
         <is>
           <t>マスター関連</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="0" t="inlineStr">
         <is>
           <t>改修確認</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" s="0" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="0" t="inlineStr">
         <is>
           <t>マスター関連</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>本番実装承認</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" s="0" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="0" t="inlineStr">
         <is>
           <t>マスター関連</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>完成検査</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" s="0" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="0" t="inlineStr">
         <is>
           <t>ユーザーへの告知</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>ToDo</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" s="0" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="0" t="inlineStr">
         <is>
           <t>ユーザーへの告知</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" s="0" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="0" t="inlineStr">
         <is>
           <t>ユーザーへの告知</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" s="0" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="0" t="inlineStr">
         <is>
           <t>改修</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="0" t="inlineStr">
         <is>
           <t>①案件</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="0" t="n">
         <v>34</v>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" s="0" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="0" t="inlineStr">
         <is>
           <t>改修</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="0" t="inlineStr">
         <is>
           <t>②要件定義/改修承認</t>
         </is>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" s="0" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="0" t="inlineStr">
         <is>
           <t>改修</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>③【CODIUM】改修確認</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" s="0" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="0" t="inlineStr">
         <is>
           <t>改修</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>④見積・発注</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" s="0" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="0" t="inlineStr">
         <is>
           <t>改修</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="0" t="inlineStr">
         <is>
           <t>⑤【開発】改修依頼中</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" s="0" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="0" t="inlineStr">
         <is>
           <t>改修</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="0" t="inlineStr">
         <is>
           <t>⑥【開発】改修確認</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" s="0" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="0" t="inlineStr">
         <is>
           <t>改修</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="0" t="inlineStr">
         <is>
           <t>⑦【ステージング】修正確認</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" s="0" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="0" t="inlineStr">
         <is>
           <t>改修</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="0" t="inlineStr">
         <is>
           <t>⑧【ステージング】本番実装承認</t>
         </is>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" s="0" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="0" t="inlineStr">
         <is>
           <t>改修</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="0" t="inlineStr">
         <is>
           <t>⑨【本番】実装依頼中</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" s="0" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="0" t="inlineStr">
         <is>
           <t>改修</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="0" t="inlineStr">
         <is>
           <t>⑩【本番】完成検査/承認</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="0" t="n">
         <v>58</v>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" s="0" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="0" t="inlineStr">
         <is>
           <t>改修</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="0" t="inlineStr">
         <is>
           <t>⑪完了済</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="0" t="n">
         <v>29</v>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" s="0" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="0" t="inlineStr">
         <is>
           <t>監査報告</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="0" t="inlineStr">
         <is>
           <t>現地監査結果</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" s="0" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="0" t="inlineStr">
         <is>
           <t>監査報告</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="0" t="inlineStr">
         <is>
           <t>パッチチェックリスト</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" s="0" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="0" t="inlineStr">
         <is>
           <t>監査報告</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="0" t="inlineStr">
         <is>
           <t>ログチェックリスト</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" s="0" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="0" t="inlineStr">
         <is>
           <t>監査報告</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="0" t="inlineStr">
         <is>
           <t>脆弱性　診断　対応</t>
         </is>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" s="0" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="0" t="inlineStr">
         <is>
           <t>監査報告</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="0" t="inlineStr">
         <is>
           <t>四半期チェックリスト</t>
         </is>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" s="0" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="0" t="inlineStr">
         <is>
           <t>承認ルール</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="0" t="inlineStr">
         <is>
           <t>承認ルール</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="C80" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" s="0" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="0" t="inlineStr">
         <is>
           <t>承認ルール</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="0" t="inlineStr">
         <is>
           <t>作業中</t>
         </is>
       </c>
-      <c r="C81" t="n">
+      <c r="C81" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" s="0" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="0" t="inlineStr">
         <is>
           <t>承認ルール</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="0" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="C82" t="n">
+      <c r="C82" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" s="0" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="0" t="inlineStr">
         <is>
           <t>新規開発</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="0" t="inlineStr">
         <is>
           <t>①案件</t>
         </is>
       </c>
-      <c r="C83" t="n">
+      <c r="C83" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" s="0" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="0" t="inlineStr">
         <is>
           <t>新規開発</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="0" t="inlineStr">
         <is>
           <t>②要件定義</t>
         </is>
       </c>
-      <c r="C84" t="n">
+      <c r="C84" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" s="0" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="0" t="inlineStr">
         <is>
           <t>新規開発</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="0" t="inlineStr">
         <is>
           <t>③【CODIUM改修確認】</t>
         </is>
       </c>
-      <c r="C85" t="n">
+      <c r="C85" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" s="0" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="0" t="inlineStr">
         <is>
           <t>新規開発</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="0" t="inlineStr">
         <is>
           <t>④見積・発注</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="C86" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" s="0" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="0" t="inlineStr">
         <is>
           <t>新規開発</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="0" t="inlineStr">
         <is>
           <t>⑤【開発版】改修依頼中</t>
         </is>
       </c>
-      <c r="C87" t="n">
+      <c r="C87" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" s="0" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="0" t="inlineStr">
         <is>
           <t>新規開発</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="0" t="inlineStr">
         <is>
           <t>⑥【開発版】改修確認</t>
         </is>
       </c>
-      <c r="C88" t="n">
+      <c r="C88" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" s="0" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="0" t="inlineStr">
         <is>
           <t>新規開発</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="0" t="inlineStr">
         <is>
           <t>⑦【開発版】本番実装承認</t>
         </is>
       </c>
-      <c r="C89" t="n">
+      <c r="C89" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" s="0" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="0" t="inlineStr">
         <is>
           <t>新規開発</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="0" t="inlineStr">
         <is>
           <t>⑧【本番】実装依頼中</t>
         </is>
       </c>
-      <c r="C90" t="n">
+      <c r="C90" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" s="0" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="0" t="inlineStr">
         <is>
           <t>新規開発</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="0" t="inlineStr">
         <is>
           <t>⑨【本番】完成検査/承認</t>
         </is>
       </c>
-      <c r="C91" t="n">
+      <c r="C91" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" s="0" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="0" t="inlineStr">
         <is>
           <t>新規開発</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="0" t="inlineStr">
         <is>
           <t>⑩完了済</t>
         </is>
       </c>
-      <c r="C92" t="n">
+      <c r="C92" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" s="0" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="0" t="inlineStr">
         <is>
           <t>操作マニュアル</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="0" t="inlineStr">
         <is>
           <t>操作マニュアル確認</t>
         </is>
       </c>
-      <c r="C93" t="n">
+      <c r="C93" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
